--- a/data/trans_orig/P15E_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P15E_R-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7817</t>
+          <t>8600</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4722</t>
+          <t>5409</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10581</t>
+          <t>11889</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19752</t>
+          <t>21558</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15650</t>
+          <t>17596</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23190</t>
+          <t>25333</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>27569</t>
+          <t>30158</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22456</t>
+          <t>25363</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31951</t>
+          <t>35363</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,54%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2791</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8650</t>
+          <t>9682</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9989</t>
+          <t>10792</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6551</t>
+          <t>7017</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14091</t>
+          <t>14754</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>15544</t>
+          <t>17283</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11162</t>
+          <t>12078</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20657</t>
+          <t>22078</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>46,54%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13372</t>
+          <t>15091</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13372</t>
+          <t>15091</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13372</t>
+          <t>15091</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>29741</t>
+          <t>32350</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29741</t>
+          <t>32350</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29741</t>
+          <t>32350</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>43113</t>
+          <t>47441</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>43113</t>
+          <t>47441</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43113</t>
+          <t>47441</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14238</t>
+          <t>15793</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10528</t>
+          <t>11791</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16853</t>
+          <t>18913</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39864</t>
+          <t>43344</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35038</t>
+          <t>38120</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43971</t>
+          <t>47164</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>54102</t>
+          <t>59137</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47733</t>
+          <t>53003</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59241</t>
+          <t>64174</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,55%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6499</t>
+          <t>7220</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10209</t>
+          <t>11222</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>13085</t>
+          <t>13310</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8978</t>
+          <t>9490</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17911</t>
+          <t>18534</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>19584</t>
+          <t>20530</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14445</t>
+          <t>15493</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25953</t>
+          <t>26664</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>33,47%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20737</t>
+          <t>23013</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20737</t>
+          <t>23013</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20737</t>
+          <t>23013</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>52949</t>
+          <t>56654</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>52949</t>
+          <t>56654</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>52949</t>
+          <t>56654</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>73686</t>
+          <t>79667</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>73686</t>
+          <t>79667</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>73686</t>
+          <t>79667</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>22055</t>
+          <t>24393</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17080</t>
+          <t>19114</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26406</t>
+          <t>28837</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>59616</t>
+          <t>64902</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>53627</t>
+          <t>58671</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64833</t>
+          <t>70528</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>81671</t>
+          <t>89295</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>74045</t>
+          <t>81785</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88323</t>
+          <t>96701</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>76,08%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>13711</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7703</t>
+          <t>9267</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17029</t>
+          <t>18990</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23074</t>
+          <t>24102</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17857</t>
+          <t>18476</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29063</t>
+          <t>30333</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>35127</t>
+          <t>37813</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>28475</t>
+          <t>30407</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>42753</t>
+          <t>45323</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>35,66%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>34109</t>
+          <t>38104</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34109</t>
+          <t>38104</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34109</t>
+          <t>38104</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>82690</t>
+          <t>89004</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>82690</t>
+          <t>89004</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>82690</t>
+          <t>89004</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>116798</t>
+          <t>127108</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>116798</t>
+          <t>127108</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>116798</t>
+          <t>127108</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
